--- a/Exp3_PTO_GRPO/eda/results/arms/stats/tables/claude-haiku-4-5/stats.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/stats/tables/claude-haiku-4-5/stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,7 +697,7 @@
         <v>0.007900000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         <v>0.008800000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="7">
@@ -769,16 +769,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.526</v>
+        <v>0.523</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="G7" t="n">
-        <v>0.422</v>
+        <v>0.244</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.0002</v>
+        <v>0.0507</v>
       </c>
       <c r="J7" t="n">
-        <v>0.046</v>
+        <v>0.013</v>
       </c>
       <c r="K7" t="n">
-        <v>0.129</v>
+        <v>0.106</v>
       </c>
       <c r="L7" t="n">
-        <v>0.026</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0018</v>
+        <v>0.0011</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="8">
@@ -905,7 +905,7 @@
         <v>0.002</v>
       </c>
       <c r="N9" t="n">
-        <v>0.011</v>
+        <v>0.0329</v>
       </c>
     </row>
     <row r="10">
@@ -963,12 +963,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -977,39 +977,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.834</v>
+        <v>0.241</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>1.038</v>
+        <v>-0.064</v>
       </c>
       <c r="G11" t="n">
-        <v>1.539</v>
+        <v>-0.107</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.3656</v>
       </c>
       <c r="J11" t="n">
-        <v>0.909</v>
+        <v>-0.183</v>
       </c>
       <c r="K11" t="n">
-        <v>1.177</v>
+        <v>0.056</v>
       </c>
       <c r="L11" t="n">
-        <v>0.383</v>
+        <v>-0.028</v>
       </c>
       <c r="M11" t="n">
-        <v>0.101</v>
+        <v>-0.0027</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.3656</v>
       </c>
     </row>
     <row r="12">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.165</v>
+        <v>1.834</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0.793</v>
+        <v>1.038</v>
       </c>
       <c r="G12" t="n">
-        <v>1.304</v>
+        <v>1.539</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.676</v>
+        <v>0.909</v>
       </c>
       <c r="K12" t="n">
-        <v>0.911</v>
+        <v>1.177</v>
       </c>
       <c r="L12" t="n">
-        <v>0.239</v>
+        <v>0.383</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.091</v>
+        <v>2.165</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0.844</v>
+        <v>0.793</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43</v>
+        <v>1.304</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.73</v>
+        <v>0.676</v>
       </c>
       <c r="K13" t="n">
-        <v>0.964</v>
+        <v>0.911</v>
       </c>
       <c r="L13" t="n">
-        <v>0.246</v>
+        <v>0.239</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0786</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1133,16 +1133,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.439</v>
+        <v>2.091</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>0.889</v>
+        <v>0.844</v>
       </c>
       <c r="G14" t="n">
-        <v>1.234</v>
+        <v>1.43</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.753</v>
+        <v>0.73</v>
       </c>
       <c r="K14" t="n">
-        <v>1.03</v>
+        <v>0.964</v>
       </c>
       <c r="L14" t="n">
-        <v>0.263</v>
+        <v>0.246</v>
       </c>
       <c r="M14" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0786</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.831</v>
+        <v>2.439</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>0.544</v>
+        <v>0.889</v>
       </c>
       <c r="G15" t="n">
-        <v>0.881</v>
+        <v>1.234</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1205,16 +1205,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.417</v>
+        <v>0.753</v>
       </c>
       <c r="K15" t="n">
-        <v>0.667</v>
+        <v>1.03</v>
       </c>
       <c r="L15" t="n">
-        <v>0.204</v>
+        <v>0.263</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0493</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1237,13 +1237,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.507</v>
+        <v>1.831</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>0.219</v>
+        <v>0.544</v>
       </c>
       <c r="G16" t="n">
         <v>0.881</v>
@@ -1257,16 +1257,16 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.171</v>
+        <v>0.417</v>
       </c>
       <c r="K16" t="n">
-        <v>0.267</v>
+        <v>0.667</v>
       </c>
       <c r="L16" t="n">
-        <v>0.208</v>
+        <v>0.204</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0233</v>
+        <v>0.0493</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.326</v>
+        <v>0.477</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>0.301</v>
+        <v>0.26</v>
       </c>
       <c r="G17" t="n">
-        <v>0.845</v>
+        <v>0.873</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1309,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.233</v>
+        <v>0.202</v>
       </c>
       <c r="K17" t="n">
-        <v>0.372</v>
+        <v>0.318</v>
       </c>
       <c r="L17" t="n">
-        <v>0.322</v>
+        <v>0.193</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0276</v>
+        <v>0.0252</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.681</v>
+        <v>0.326</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>1.05</v>
+        <v>0.301</v>
       </c>
       <c r="G18" t="n">
-        <v>1.228</v>
+        <v>0.845</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1361,16 +1361,16 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.887</v>
+        <v>0.233</v>
       </c>
       <c r="K18" t="n">
-        <v>1.221</v>
+        <v>0.372</v>
       </c>
       <c r="L18" t="n">
-        <v>0.334</v>
+        <v>0.322</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1051</v>
+        <v>0.0276</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.988</v>
+        <v>1.681</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.027</v>
+        <v>1.05</v>
       </c>
       <c r="G19" t="n">
-        <v>1.594</v>
+        <v>1.228</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1413,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.896</v>
+        <v>0.887</v>
       </c>
       <c r="K19" t="n">
-        <v>1.158</v>
+        <v>1.221</v>
       </c>
       <c r="L19" t="n">
-        <v>0.408</v>
+        <v>0.334</v>
       </c>
       <c r="M19" t="n">
-        <v>0.097</v>
+        <v>0.1051</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1431,12 +1431,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.83</v>
+        <v>1.988</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>1.036</v>
+        <v>1.027</v>
       </c>
       <c r="G20" t="n">
-        <v>1.653</v>
+        <v>1.594</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1465,16 +1465,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.912</v>
+        <v>0.896</v>
       </c>
       <c r="K20" t="n">
-        <v>1.157</v>
+        <v>1.158</v>
       </c>
       <c r="L20" t="n">
-        <v>0.401</v>
+        <v>0.408</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1046</v>
+        <v>0.097</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1483,12 +1483,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.117</v>
+        <v>0.198</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>0.838</v>
+        <v>0.605</v>
       </c>
       <c r="G21" t="n">
-        <v>1.177</v>
+        <v>1.106</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1517,16 +1517,16 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.694</v>
+        <v>0.49</v>
       </c>
       <c r="K21" t="n">
-        <v>0.983</v>
+        <v>0.707</v>
       </c>
       <c r="L21" t="n">
-        <v>0.253</v>
+        <v>0.428</v>
       </c>
       <c r="M21" t="n">
-        <v>0.077</v>
+        <v>0.0675</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1549,16 +1549,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.042</v>
+        <v>1.83</v>
       </c>
       <c r="E22" t="n">
         <v>10</v>
       </c>
       <c r="F22" t="n">
-        <v>0.767</v>
+        <v>1.036</v>
       </c>
       <c r="G22" t="n">
-        <v>1.287</v>
+        <v>1.653</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1569,16 +1569,16 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.65</v>
+        <v>0.912</v>
       </c>
       <c r="K22" t="n">
-        <v>0.885</v>
+        <v>1.157</v>
       </c>
       <c r="L22" t="n">
-        <v>0.224</v>
+        <v>0.401</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0706</v>
+        <v>0.1046</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.464</v>
+        <v>2.117</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>0.609</v>
+        <v>0.838</v>
       </c>
       <c r="G23" t="n">
-        <v>0.899</v>
+        <v>1.177</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1621,16 +1621,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.479</v>
+        <v>0.694</v>
       </c>
       <c r="K23" t="n">
-        <v>0.747</v>
+        <v>0.983</v>
       </c>
       <c r="L23" t="n">
-        <v>0.196</v>
+        <v>0.253</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0576</v>
+        <v>0.077</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.839</v>
+        <v>2.042</v>
       </c>
       <c r="E24" t="n">
         <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>0.513</v>
+        <v>0.767</v>
       </c>
       <c r="G24" t="n">
-        <v>0.88</v>
+        <v>1.287</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1673,16 +1673,16 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.393</v>
+        <v>0.65</v>
       </c>
       <c r="K24" t="n">
-        <v>0.62</v>
+        <v>0.885</v>
       </c>
       <c r="L24" t="n">
-        <v>0.271</v>
+        <v>0.224</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0493</v>
+        <v>0.0706</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1705,36 +1705,36 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.52</v>
+        <v>2.464</v>
       </c>
       <c r="E25" t="n">
         <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>0.113</v>
+        <v>0.609</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.899</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.073</v>
+        <v>0.479</v>
       </c>
       <c r="K25" t="n">
-        <v>0.154</v>
+        <v>0.747</v>
       </c>
       <c r="L25" t="n">
-        <v>0.108</v>
+        <v>0.196</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0119</v>
+        <v>0.0576</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1757,16 +1757,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.364</v>
+        <v>1.839</v>
       </c>
       <c r="E26" t="n">
         <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>0.461</v>
+        <v>0.513</v>
       </c>
       <c r="G26" t="n">
-        <v>0.992</v>
+        <v>0.88</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1777,13 +1777,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.365</v>
+        <v>0.393</v>
       </c>
       <c r="K26" t="n">
-        <v>0.553</v>
+        <v>0.62</v>
       </c>
       <c r="L26" t="n">
-        <v>0.511</v>
+        <v>0.271</v>
       </c>
       <c r="M26" t="n">
         <v>0.0493</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1809,39 +1809,39 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.673</v>
+        <v>0.502</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.967</v>
+        <v>0.111</v>
       </c>
       <c r="G27" t="n">
-        <v>1.335</v>
+        <v>0.426</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.823</v>
+        <v>0.059</v>
       </c>
       <c r="K27" t="n">
-        <v>1.104</v>
+        <v>0.164</v>
       </c>
       <c r="L27" t="n">
-        <v>0.323</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0121</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="28">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1861,16 +1861,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.987</v>
+        <v>0.364</v>
       </c>
       <c r="E28" t="n">
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>1.106</v>
+        <v>0.461</v>
       </c>
       <c r="G28" t="n">
-        <v>1.718</v>
+        <v>0.992</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.98</v>
+        <v>0.365</v>
       </c>
       <c r="K28" t="n">
-        <v>1.239</v>
+        <v>0.553</v>
       </c>
       <c r="L28" t="n">
-        <v>0.468</v>
+        <v>0.511</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1115</v>
+        <v>0.0493</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -1899,12 +1899,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.834</v>
+        <v>1.673</v>
       </c>
       <c r="E29" t="n">
         <v>10</v>
       </c>
       <c r="F29" t="n">
-        <v>0.833</v>
+        <v>0.967</v>
       </c>
       <c r="G29" t="n">
-        <v>1.124</v>
+        <v>1.335</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1933,16 +1933,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.823</v>
       </c>
       <c r="K29" t="n">
-        <v>0.981</v>
+        <v>1.104</v>
       </c>
       <c r="L29" t="n">
-        <v>0.349</v>
+        <v>0.323</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0883</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -1951,12 +1951,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2.149</v>
+        <v>1.987</v>
       </c>
       <c r="E30" t="n">
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>0.701</v>
+        <v>1.106</v>
       </c>
       <c r="G30" t="n">
-        <v>0.973</v>
+        <v>1.718</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1985,16 +1985,16 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="K30" t="n">
-        <v>0.844</v>
+        <v>1.239</v>
       </c>
       <c r="L30" t="n">
-        <v>0.227</v>
+        <v>0.468</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0717</v>
+        <v>0.1115</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2003,12 +2003,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2017,39 +2017,39 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.099</v>
+        <v>0.208</v>
       </c>
       <c r="E31" t="n">
         <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>0.708</v>
+        <v>0.057</v>
       </c>
       <c r="G31" t="n">
-        <v>0.957</v>
+        <v>0.102</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.059</v>
       </c>
       <c r="K31" t="n">
-        <v>0.853</v>
+        <v>0.165</v>
       </c>
       <c r="L31" t="n">
-        <v>0.23</v>
+        <v>0.039</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0728</v>
+        <v>0.0053</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="32">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.464</v>
+        <v>1.834</v>
       </c>
       <c r="E32" t="n">
         <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>0.72</v>
+        <v>0.833</v>
       </c>
       <c r="G32" t="n">
-        <v>1.055</v>
+        <v>1.124</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.583</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>0.859</v>
+        <v>0.981</v>
       </c>
       <c r="L32" t="n">
-        <v>0.222</v>
+        <v>0.349</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0717</v>
+        <v>0.0883</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2121,36 +2121,36 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.852</v>
+        <v>2.149</v>
       </c>
       <c r="E33" t="n">
         <v>10</v>
       </c>
       <c r="F33" t="n">
-        <v>0.297</v>
+        <v>0.701</v>
       </c>
       <c r="G33" t="n">
-        <v>0.52</v>
+        <v>0.973</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.177</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>0.409</v>
+        <v>0.844</v>
       </c>
       <c r="L33" t="n">
-        <v>0.131</v>
+        <v>0.227</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0282</v>
+        <v>0.0717</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2173,36 +2173,36 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.523</v>
+        <v>2.099</v>
       </c>
       <c r="E34" t="n">
         <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>0.161</v>
+        <v>0.708</v>
       </c>
       <c r="G34" t="n">
-        <v>0.64</v>
+        <v>0.957</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.113</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.213</v>
+        <v>0.853</v>
       </c>
       <c r="L34" t="n">
-        <v>0.125</v>
+        <v>0.23</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0141</v>
+        <v>0.0728</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2225,36 +2225,36 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.37</v>
+        <v>2.464</v>
       </c>
       <c r="E35" t="n">
         <v>10</v>
       </c>
       <c r="F35" t="n">
-        <v>0.21</v>
+        <v>0.72</v>
       </c>
       <c r="G35" t="n">
-        <v>0.48</v>
+        <v>1.055</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.125</v>
+        <v>0.583</v>
       </c>
       <c r="K35" t="n">
-        <v>0.296</v>
+        <v>0.859</v>
       </c>
       <c r="L35" t="n">
-        <v>0.247</v>
+        <v>0.222</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0247</v>
+        <v>0.0717</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2277,36 +2277,36 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.683</v>
+        <v>1.852</v>
       </c>
       <c r="E36" t="n">
         <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>0.921</v>
+        <v>0.297</v>
       </c>
       <c r="G36" t="n">
-        <v>1.043</v>
+        <v>0.52</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.75</v>
+        <v>0.177</v>
       </c>
       <c r="K36" t="n">
-        <v>1.094</v>
+        <v>0.409</v>
       </c>
       <c r="L36" t="n">
-        <v>0.337</v>
+        <v>0.131</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1005</v>
+        <v>0.0282</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2329,36 +2329,36 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.984</v>
+        <v>0.509</v>
       </c>
       <c r="E37" t="n">
         <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>0.746</v>
+        <v>0.178</v>
       </c>
       <c r="G37" t="n">
-        <v>1.039</v>
+        <v>0.626</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.607</v>
+        <v>0.121</v>
       </c>
       <c r="K37" t="n">
-        <v>0.887</v>
+        <v>0.236</v>
       </c>
       <c r="L37" t="n">
-        <v>0.328</v>
+        <v>0.11</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0762</v>
+        <v>0.0149</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -2367,50 +2367,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>best</t>
+          <t>final</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.861</v>
+        <v>0.37</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>0.776</v>
+        <v>0.21</v>
       </c>
       <c r="G38" t="n">
-        <v>1.459</v>
+        <v>0.48</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.671</v>
+        <v>0.125</v>
       </c>
       <c r="K38" t="n">
-        <v>0.88</v>
+        <v>0.296</v>
       </c>
       <c r="L38" t="n">
-        <v>0.103</v>
+        <v>0.247</v>
       </c>
       <c r="M38" t="n">
-        <v>0.0264</v>
+        <v>0.0247</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -2419,30 +2419,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>best</t>
+          <t>final</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.222</v>
+        <v>1.683</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>0.635</v>
+        <v>0.921</v>
       </c>
       <c r="G39" t="n">
-        <v>1.082</v>
+        <v>1.043</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2453,16 +2453,16 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.518</v>
+        <v>0.75</v>
       </c>
       <c r="K39" t="n">
-        <v>0.752</v>
+        <v>1.094</v>
       </c>
       <c r="L39" t="n">
-        <v>0.109</v>
+        <v>0.337</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0295</v>
+        <v>0.1005</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -2471,30 +2471,30 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>best</t>
+          <t>final</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2.087</v>
+        <v>1.984</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>0.612</v>
+        <v>0.746</v>
       </c>
       <c r="G40" t="n">
-        <v>1.011</v>
+        <v>1.039</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2505,16 +2505,16 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.49</v>
+        <v>0.607</v>
       </c>
       <c r="K40" t="n">
-        <v>0.727</v>
+        <v>0.887</v>
       </c>
       <c r="L40" t="n">
-        <v>0.058</v>
+        <v>0.328</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0224</v>
+        <v>0.0762</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2523,53 +2523,53 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>best</t>
+          <t>final</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.521</v>
+        <v>0.189</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>0.46</v>
+        <v>0.254</v>
       </c>
       <c r="G41" t="n">
-        <v>0.677</v>
+        <v>0.391</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="J41" t="n">
-        <v>0.326</v>
+        <v>0.125</v>
       </c>
       <c r="K41" t="n">
-        <v>0.595</v>
+        <v>0.379</v>
       </c>
       <c r="L41" t="n">
-        <v>0.036</v>
+        <v>0.135</v>
       </c>
       <c r="M41" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.019</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="42">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2589,16 +2589,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.888</v>
+        <v>1.861</v>
       </c>
       <c r="E42" t="n">
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>0.495</v>
+        <v>0.776</v>
       </c>
       <c r="G42" t="n">
-        <v>0.894</v>
+        <v>1.459</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2609,16 +2609,16 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.388</v>
+        <v>0.671</v>
       </c>
       <c r="K42" t="n">
-        <v>0.599</v>
+        <v>0.88</v>
       </c>
       <c r="L42" t="n">
-        <v>0.033</v>
+        <v>0.103</v>
       </c>
       <c r="M42" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0264</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2641,39 +2641,39 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.526</v>
+        <v>2.222</v>
       </c>
       <c r="E43" t="n">
         <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>0.075</v>
+        <v>0.635</v>
       </c>
       <c r="G43" t="n">
-        <v>0.33</v>
+        <v>1.082</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.0021</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.031</v>
+        <v>0.518</v>
       </c>
       <c r="K43" t="n">
-        <v>0.121</v>
+        <v>0.752</v>
       </c>
       <c r="L43" t="n">
-        <v>0.026</v>
+        <v>0.109</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0018</v>
+        <v>0.0295</v>
       </c>
       <c r="N43" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2693,39 +2693,39 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.384</v>
+        <v>2.087</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>0.024</v>
+        <v>0.612</v>
       </c>
       <c r="G44" t="n">
-        <v>0.06900000000000001</v>
+        <v>1.011</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4946</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.043</v>
+        <v>0.49</v>
       </c>
       <c r="K44" t="n">
-        <v>0.092</v>
+        <v>0.727</v>
       </c>
       <c r="L44" t="n">
-        <v>0.612</v>
+        <v>0.058</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0635</v>
+        <v>0.0224</v>
       </c>
       <c r="N44" t="n">
-        <v>0.4946</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2745,36 +2745,36 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.694</v>
+        <v>2.521</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>0.883</v>
+        <v>0.46</v>
       </c>
       <c r="G45" t="n">
-        <v>1.268</v>
+        <v>0.677</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.746</v>
+        <v>0.326</v>
       </c>
       <c r="K45" t="n">
-        <v>1.021</v>
+        <v>0.595</v>
       </c>
       <c r="L45" t="n">
-        <v>0.005</v>
+        <v>0.036</v>
       </c>
       <c r="M45" t="n">
-        <v>0.002</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2797,16 +2797,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2.028</v>
+        <v>1.888</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>0.668</v>
+        <v>0.495</v>
       </c>
       <c r="G46" t="n">
-        <v>1.273</v>
+        <v>0.894</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2817,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.572</v>
+        <v>0.388</v>
       </c>
       <c r="K46" t="n">
-        <v>0.772</v>
+        <v>0.599</v>
       </c>
       <c r="L46" t="n">
-        <v>0.202</v>
+        <v>0.033</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0508</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -2835,12 +2835,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2849,50 +2849,50 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.834</v>
+        <v>0.523</v>
       </c>
       <c r="E47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>1.078</v>
+        <v>0.081</v>
       </c>
       <c r="G47" t="n">
-        <v>1.466</v>
+        <v>0.325</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="K47" t="n">
-        <v>1.228</v>
+        <v>0.133</v>
       </c>
       <c r="L47" t="n">
-        <v>0.383</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>0.101</v>
+        <v>0.0011</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2901,50 +2901,50 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.165</v>
+        <v>0.384</v>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>0.723</v>
+        <v>0.024</v>
       </c>
       <c r="G48" t="n">
-        <v>1.17</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>0.4946</v>
       </c>
       <c r="J48" t="n">
-        <v>0.603</v>
+        <v>-0.043</v>
       </c>
       <c r="K48" t="n">
-        <v>0.852</v>
+        <v>0.092</v>
       </c>
       <c r="L48" t="n">
-        <v>0.239</v>
+        <v>0.612</v>
       </c>
       <c r="M48" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0635</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>0.8385</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.091</v>
+        <v>1.694</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>0.701</v>
+        <v>0.883</v>
       </c>
       <c r="G49" t="n">
-        <v>1.004</v>
+        <v>1.268</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2973,16 +2973,16 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.746</v>
       </c>
       <c r="K49" t="n">
-        <v>0.839</v>
+        <v>1.021</v>
       </c>
       <c r="L49" t="n">
-        <v>0.246</v>
+        <v>0.005</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0786</v>
+        <v>0.002</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -2991,12 +2991,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3005,16 +3005,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.439</v>
+        <v>2.028</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>0.766</v>
+        <v>0.668</v>
       </c>
       <c r="G50" t="n">
-        <v>1.041</v>
+        <v>1.273</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3025,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.623</v>
+        <v>0.572</v>
       </c>
       <c r="K50" t="n">
-        <v>0.917</v>
+        <v>0.772</v>
       </c>
       <c r="L50" t="n">
-        <v>0.263</v>
+        <v>0.202</v>
       </c>
       <c r="M50" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0508</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3043,12 +3043,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3057,39 +3057,39 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.831</v>
+        <v>0.241</v>
       </c>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>0.552</v>
+        <v>0.044</v>
       </c>
       <c r="G51" t="n">
-        <v>1.013</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>0.4192</v>
       </c>
       <c r="J51" t="n">
-        <v>0.443</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>0.659</v>
+        <v>0.164</v>
       </c>
       <c r="L51" t="n">
-        <v>0.204</v>
+        <v>-0.028</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0493</v>
+        <v>-0.0027</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>0.8385</v>
       </c>
     </row>
     <row r="52">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3109,36 +3109,36 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.507</v>
+        <v>1.834</v>
       </c>
       <c r="E52" t="n">
         <v>7</v>
       </c>
       <c r="F52" t="n">
-        <v>0.161</v>
+        <v>1.078</v>
       </c>
       <c r="G52" t="n">
-        <v>0.736</v>
+        <v>1.466</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.12</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>0.206</v>
+        <v>1.228</v>
       </c>
       <c r="L52" t="n">
-        <v>0.208</v>
+        <v>0.383</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0233</v>
+        <v>0.101</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3161,36 +3161,36 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.326</v>
+        <v>2.165</v>
       </c>
       <c r="E53" t="n">
         <v>7</v>
       </c>
       <c r="F53" t="n">
-        <v>0.253</v>
+        <v>0.723</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6840000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.183</v>
+        <v>0.603</v>
       </c>
       <c r="K53" t="n">
-        <v>0.329</v>
+        <v>0.852</v>
       </c>
       <c r="L53" t="n">
-        <v>0.322</v>
+        <v>0.239</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0276</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3213,16 +3213,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1.681</v>
+        <v>2.091</v>
       </c>
       <c r="E54" t="n">
         <v>7</v>
       </c>
       <c r="F54" t="n">
-        <v>1.188</v>
+        <v>0.701</v>
       </c>
       <c r="G54" t="n">
-        <v>1.403</v>
+        <v>1.004</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3233,16 +3233,16 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1.025</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>1.362</v>
+        <v>0.839</v>
       </c>
       <c r="L54" t="n">
-        <v>0.334</v>
+        <v>0.246</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1051</v>
+        <v>0.0786</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3265,16 +3265,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1.988</v>
+        <v>2.439</v>
       </c>
       <c r="E55" t="n">
         <v>7</v>
       </c>
       <c r="F55" t="n">
-        <v>0.968</v>
+        <v>0.766</v>
       </c>
       <c r="G55" t="n">
-        <v>1.338</v>
+        <v>1.041</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3285,16 +3285,16 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.822</v>
+        <v>0.623</v>
       </c>
       <c r="K55" t="n">
-        <v>1.112</v>
+        <v>0.917</v>
       </c>
       <c r="L55" t="n">
-        <v>0.408</v>
+        <v>0.263</v>
       </c>
       <c r="M55" t="n">
-        <v>0.097</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -3303,12 +3303,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3317,16 +3317,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1.83</v>
+        <v>1.831</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
-        <v>1.091</v>
+        <v>0.552</v>
       </c>
       <c r="G56" t="n">
-        <v>1.621</v>
+        <v>1.013</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3337,16 +3337,16 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.962</v>
+        <v>0.443</v>
       </c>
       <c r="K56" t="n">
-        <v>1.225</v>
+        <v>0.659</v>
       </c>
       <c r="L56" t="n">
-        <v>0.401</v>
+        <v>0.204</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1046</v>
+        <v>0.0493</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -3355,12 +3355,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3369,36 +3369,36 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.117</v>
+        <v>0.477</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
-        <v>0.827</v>
+        <v>0.199</v>
       </c>
       <c r="G57" t="n">
-        <v>1.15</v>
+        <v>0.754</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.148</v>
       </c>
       <c r="K57" t="n">
-        <v>0.974</v>
+        <v>0.251</v>
       </c>
       <c r="L57" t="n">
-        <v>0.253</v>
+        <v>0.193</v>
       </c>
       <c r="M57" t="n">
-        <v>0.077</v>
+        <v>0.0252</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -3407,12 +3407,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3421,36 +3421,36 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.042</v>
+        <v>0.326</v>
       </c>
       <c r="E58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F58" t="n">
-        <v>0.806</v>
+        <v>0.253</v>
       </c>
       <c r="G58" t="n">
-        <v>1.316</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.68</v>
+        <v>0.183</v>
       </c>
       <c r="K58" t="n">
-        <v>0.925</v>
+        <v>0.329</v>
       </c>
       <c r="L58" t="n">
-        <v>0.224</v>
+        <v>0.322</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0706</v>
+        <v>0.0276</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -3459,12 +3459,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2.464</v>
+        <v>1.681</v>
       </c>
       <c r="E59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F59" t="n">
-        <v>0.635</v>
+        <v>1.188</v>
       </c>
       <c r="G59" t="n">
-        <v>0.911</v>
+        <v>1.403</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3493,16 +3493,16 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0.495</v>
+        <v>1.025</v>
       </c>
       <c r="K59" t="n">
-        <v>0.781</v>
+        <v>1.362</v>
       </c>
       <c r="L59" t="n">
-        <v>0.196</v>
+        <v>0.334</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0576</v>
+        <v>0.1051</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -3511,12 +3511,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3525,16 +3525,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.839</v>
+        <v>1.988</v>
       </c>
       <c r="E60" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.968</v>
       </c>
       <c r="G60" t="n">
-        <v>0.969</v>
+        <v>1.338</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3545,16 +3545,16 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.445</v>
+        <v>0.822</v>
       </c>
       <c r="K60" t="n">
-        <v>0.669</v>
+        <v>1.112</v>
       </c>
       <c r="L60" t="n">
-        <v>0.271</v>
+        <v>0.408</v>
       </c>
       <c r="M60" t="n">
-        <v>0.0493</v>
+        <v>0.097</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -3563,12 +3563,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3577,16 +3577,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.52</v>
+        <v>0.198</v>
       </c>
       <c r="E61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
-        <v>0.118</v>
+        <v>0.427</v>
       </c>
       <c r="G61" t="n">
-        <v>0.535</v>
+        <v>0.659</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3597,16 +3597,16 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.075</v>
+        <v>0.294</v>
       </c>
       <c r="K61" t="n">
-        <v>0.164</v>
+        <v>0.551</v>
       </c>
       <c r="L61" t="n">
-        <v>0.108</v>
+        <v>0.428</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0119</v>
+        <v>0.0675</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3629,16 +3629,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.364</v>
+        <v>1.83</v>
       </c>
       <c r="E62" t="n">
         <v>9</v>
       </c>
       <c r="F62" t="n">
-        <v>0.382</v>
+        <v>1.091</v>
       </c>
       <c r="G62" t="n">
-        <v>0.895</v>
+        <v>1.621</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3649,16 +3649,16 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3</v>
+        <v>0.962</v>
       </c>
       <c r="K62" t="n">
-        <v>0.465</v>
+        <v>1.225</v>
       </c>
       <c r="L62" t="n">
-        <v>0.511</v>
+        <v>0.401</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0493</v>
+        <v>0.1046</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3681,16 +3681,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.673</v>
+        <v>2.117</v>
       </c>
       <c r="E63" t="n">
         <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>1.048</v>
+        <v>0.827</v>
       </c>
       <c r="G63" t="n">
-        <v>1.257</v>
+        <v>1.15</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3701,16 +3701,16 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0.885</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>1.215</v>
+        <v>0.974</v>
       </c>
       <c r="L63" t="n">
-        <v>0.323</v>
+        <v>0.253</v>
       </c>
       <c r="M63" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3733,16 +3733,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.987</v>
+        <v>2.042</v>
       </c>
       <c r="E64" t="n">
         <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>1.135</v>
+        <v>0.806</v>
       </c>
       <c r="G64" t="n">
-        <v>1.827</v>
+        <v>1.316</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3753,16 +3753,16 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1.015</v>
+        <v>0.68</v>
       </c>
       <c r="K64" t="n">
-        <v>1.259</v>
+        <v>0.925</v>
       </c>
       <c r="L64" t="n">
-        <v>0.468</v>
+        <v>0.224</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1115</v>
+        <v>0.0706</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -3771,12 +3771,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3785,16 +3785,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.834</v>
+        <v>2.464</v>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F65" t="n">
-        <v>0.902</v>
+        <v>0.635</v>
       </c>
       <c r="G65" t="n">
-        <v>1.306</v>
+        <v>0.911</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3805,16 +3805,16 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.761</v>
+        <v>0.495</v>
       </c>
       <c r="K65" t="n">
-        <v>1.045</v>
+        <v>0.781</v>
       </c>
       <c r="L65" t="n">
-        <v>0.349</v>
+        <v>0.196</v>
       </c>
       <c r="M65" t="n">
-        <v>0.0883</v>
+        <v>0.0576</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -3823,12 +3823,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3837,16 +3837,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2.149</v>
+        <v>1.839</v>
       </c>
       <c r="E66" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F66" t="n">
-        <v>0.659</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>0.866</v>
+        <v>0.969</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3857,16 +3857,16 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0.508</v>
+        <v>0.445</v>
       </c>
       <c r="K66" t="n">
-        <v>0.802</v>
+        <v>0.669</v>
       </c>
       <c r="L66" t="n">
-        <v>0.227</v>
+        <v>0.271</v>
       </c>
       <c r="M66" t="n">
-        <v>0.0717</v>
+        <v>0.0493</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -3875,12 +3875,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3889,50 +3889,50 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2.099</v>
+        <v>0.502</v>
       </c>
       <c r="E67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F67" t="n">
-        <v>0.674</v>
+        <v>0.122</v>
       </c>
       <c r="G67" t="n">
-        <v>0.868</v>
+        <v>0.453</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J67" t="n">
-        <v>0.517</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>0.826</v>
+        <v>0.177</v>
       </c>
       <c r="L67" t="n">
-        <v>0.23</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M67" t="n">
-        <v>0.0728</v>
+        <v>0.0121</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3941,36 +3941,36 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2.464</v>
+        <v>0.364</v>
       </c>
       <c r="E68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F68" t="n">
-        <v>0.63</v>
+        <v>0.382</v>
       </c>
       <c r="G68" t="n">
-        <v>0.794</v>
+        <v>0.895</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="K68" t="n">
-        <v>0.783</v>
+        <v>0.465</v>
       </c>
       <c r="L68" t="n">
-        <v>0.222</v>
+        <v>0.511</v>
       </c>
       <c r="M68" t="n">
-        <v>0.0717</v>
+        <v>0.0493</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -3979,12 +3979,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3993,36 +3993,36 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.852</v>
+        <v>1.673</v>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F69" t="n">
-        <v>0.362</v>
+        <v>1.048</v>
       </c>
       <c r="G69" t="n">
-        <v>0.642</v>
+        <v>1.257</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0.253</v>
+        <v>0.885</v>
       </c>
       <c r="K69" t="n">
-        <v>0.474</v>
+        <v>1.215</v>
       </c>
       <c r="L69" t="n">
-        <v>0.131</v>
+        <v>0.323</v>
       </c>
       <c r="M69" t="n">
-        <v>0.0282</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -4031,12 +4031,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4045,50 +4045,50 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.523</v>
+        <v>1.987</v>
       </c>
       <c r="E70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F70" t="n">
-        <v>0.09</v>
+        <v>1.135</v>
       </c>
       <c r="G70" t="n">
-        <v>0.318</v>
+        <v>1.827</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0.034</v>
+        <v>1.015</v>
       </c>
       <c r="K70" t="n">
-        <v>0.145</v>
+        <v>1.259</v>
       </c>
       <c r="L70" t="n">
-        <v>0.125</v>
+        <v>0.468</v>
       </c>
       <c r="M70" t="n">
-        <v>0.0141</v>
+        <v>0.1115</v>
       </c>
       <c r="N70" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4097,39 +4097,39 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.37</v>
+        <v>0.208</v>
       </c>
       <c r="E71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F71" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.515</v>
+        <v>0</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>0.128</v>
+        <v>-0.115</v>
       </c>
       <c r="K71" t="n">
-        <v>0.294</v>
+        <v>0.104</v>
       </c>
       <c r="L71" t="n">
-        <v>0.247</v>
+        <v>0.039</v>
       </c>
       <c r="M71" t="n">
-        <v>0.0247</v>
+        <v>0.0053</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4149,16 +4149,16 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.683</v>
+        <v>1.834</v>
       </c>
       <c r="E72" t="n">
         <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>1.025</v>
+        <v>0.902</v>
       </c>
       <c r="G72" t="n">
-        <v>1.164</v>
+        <v>1.306</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4169,16 +4169,16 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0.844</v>
+        <v>0.761</v>
       </c>
       <c r="K72" t="n">
-        <v>1.204</v>
+        <v>1.045</v>
       </c>
       <c r="L72" t="n">
-        <v>0.337</v>
+        <v>0.349</v>
       </c>
       <c r="M72" t="n">
-        <v>0.1005</v>
+        <v>0.0883</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4201,39 +4201,455 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.984</v>
+        <v>2.149</v>
       </c>
       <c r="E73" t="n">
         <v>7</v>
       </c>
       <c r="F73" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CSQ-8</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2.099</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MI-SAT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2.464</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MITI</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1.852</v>
+      </c>
+      <c r="E76" t="n">
+        <v>7</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.0282</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="E77" t="n">
+        <v>7</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.0061</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MICI</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1.683</v>
+      </c>
+      <c r="E79" t="n">
+        <v>7</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="E80" t="n">
+        <v>7</v>
+      </c>
+      <c r="F80" t="n">
         <v>0.778</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G80" t="n">
         <v>1.194</v>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>large</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
         <v>0.651</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K80" t="n">
         <v>0.912</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L80" t="n">
         <v>0.328</v>
       </c>
-      <c r="M73" t="n">
+      <c r="M80" t="n">
         <v>0.0762</v>
       </c>
-      <c r="N73" t="n">
-        <v>0</v>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="E81" t="n">
+        <v>7</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.1576</v>
       </c>
     </row>
   </sheetData>
@@ -4247,7 +4663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4434,19 +4850,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>66.8348</v>
+        <v>36.6358</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0696</v>
+        <v>0.0394</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
@@ -4533,22 +4949,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>368.6102</v>
+        <v>8.956099999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.5363</v>
       </c>
       <c r="E11" t="n">
-        <v>0.384</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F11" t="n">
         <v>11</v>
@@ -4565,17 +4981,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>277.0336</v>
+        <v>368.6102</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2886</v>
+        <v>0.384</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
@@ -4592,17 +5008,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>282.3218</v>
+        <v>277.0336</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2941</v>
+        <v>0.2886</v>
       </c>
       <c r="F13" t="n">
         <v>11</v>
@@ -4619,17 +5035,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>304.035</v>
+        <v>282.3218</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3167</v>
+        <v>0.2941</v>
       </c>
       <c r="F14" t="n">
         <v>11</v>
@@ -4646,17 +5062,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>135.0381</v>
+        <v>304.035</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1407</v>
+        <v>0.3167</v>
       </c>
       <c r="F15" t="n">
         <v>11</v>
@@ -4673,17 +5089,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>202.1029</v>
+        <v>135.0381</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2105</v>
+        <v>0.1407</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
@@ -4700,23 +5116,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>151.4486</v>
+        <v>171.6621</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1578</v>
+        <v>0.1807</v>
       </c>
       <c r="F17" t="n">
         <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
@@ -4727,17 +5143,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>335.3761</v>
+        <v>151.4486</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3494</v>
+        <v>0.1578</v>
       </c>
       <c r="F18" t="n">
         <v>11</v>
@@ -4754,17 +5170,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>351.3549</v>
+        <v>335.3761</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.366</v>
+        <v>0.3494</v>
       </c>
       <c r="F19" t="n">
         <v>11</v>
@@ -4776,22 +5192,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>377.8588</v>
+        <v>351.3549</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3936</v>
+        <v>0.366</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
@@ -4803,22 +5219,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>263.2663</v>
+        <v>227.3061</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2742</v>
+        <v>0.2368</v>
       </c>
       <c r="F21" t="n">
         <v>11</v>
@@ -4835,17 +5251,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>228.99</v>
+        <v>377.8588</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2385</v>
+        <v>0.3936</v>
       </c>
       <c r="F22" t="n">
         <v>11</v>
@@ -4862,17 +5278,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>191.3091</v>
+        <v>263.2663</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1993</v>
+        <v>0.2742</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
@@ -4889,17 +5305,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>193.15</v>
+        <v>228.99</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2012</v>
+        <v>0.2385</v>
       </c>
       <c r="F24" t="n">
         <v>11</v>
@@ -4916,17 +5332,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>59.6523</v>
+        <v>191.3091</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0621</v>
+        <v>0.1993</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
@@ -4943,17 +5359,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>273.176</v>
+        <v>193.15</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2846</v>
+        <v>0.2012</v>
       </c>
       <c r="F26" t="n">
         <v>11</v>
@@ -4970,23 +5386,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>282.9041</v>
+        <v>31.0736</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2947</v>
+        <v>0.0366</v>
       </c>
       <c r="F27" t="n">
         <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28">
@@ -4997,17 +5413,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>436.8634</v>
+        <v>273.176</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4551</v>
+        <v>0.2846</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
@@ -5019,22 +5435,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>256.2686</v>
+        <v>282.9041</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2669</v>
+        <v>0.2947</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
@@ -5046,22 +5462,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>209.1506</v>
+        <v>436.8634</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2179</v>
+        <v>0.4551</v>
       </c>
       <c r="F30" t="n">
         <v>11</v>
@@ -5073,22 +5489,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>199.1087</v>
+        <v>23.1168</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.0103</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2074</v>
+        <v>0.0241</v>
       </c>
       <c r="F31" t="n">
         <v>11</v>
@@ -5105,17 +5521,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>197.6735</v>
+        <v>256.2686</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2059</v>
+        <v>0.2669</v>
       </c>
       <c r="F32" t="n">
         <v>11</v>
@@ -5132,17 +5548,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>76.4301</v>
+        <v>209.1506</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0796</v>
+        <v>0.2179</v>
       </c>
       <c r="F33" t="n">
         <v>11</v>
@@ -5159,17 +5575,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>77.9794</v>
+        <v>199.1087</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.2074</v>
       </c>
       <c r="F34" t="n">
         <v>11</v>
@@ -5186,17 +5602,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>83.9836</v>
+        <v>197.6735</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.2059</v>
       </c>
       <c r="F35" t="n">
         <v>11</v>
@@ -5213,17 +5629,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>252.6374</v>
+        <v>76.4301</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2632</v>
+        <v>0.0796</v>
       </c>
       <c r="F36" t="n">
         <v>11</v>
@@ -5240,23 +5656,131 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>220.7438</v>
+        <v>74.9162</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2299</v>
+        <v>0.0892</v>
       </c>
       <c r="F37" t="n">
         <v>11</v>
       </c>
       <c r="G37" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MICI</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>83.9836</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11</v>
+      </c>
+      <c r="G38" t="n">
         <v>96</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>252.6374</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11</v>
+      </c>
+      <c r="G39" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>220.7438</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.2299</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11</v>
+      </c>
+      <c r="G40" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>27.8583</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="F41" t="n">
+        <v>11</v>
+      </c>
+      <c r="G41" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -6571,7 +7095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6738,13 +7262,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0255</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0018</v>
+        <v>0.0011</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
@@ -6825,22 +7349,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3833</v>
+        <v>-0.0282</v>
       </c>
       <c r="D11" t="n">
-        <v>0.101</v>
+        <v>-0.0027</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -6854,17 +7378,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2386</v>
+        <v>0.3833</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
@@ -6878,17 +7402,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2459</v>
+        <v>0.2386</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0786</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
@@ -6902,17 +7426,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.263</v>
+        <v>0.2459</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0786</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -6926,14 +7450,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2043</v>
+        <v>0.263</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0493</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E15" t="n">
         <v>9</v>
@@ -6950,14 +7474,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2084</v>
+        <v>0.2043</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0233</v>
+        <v>0.0493</v>
       </c>
       <c r="E16" t="n">
         <v>9</v>
@@ -6974,17 +7498,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3216</v>
+        <v>0.1933</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0276</v>
+        <v>0.0252</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
@@ -6998,17 +7522,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.3339</v>
+        <v>0.3216</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1051</v>
+        <v>0.0276</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
@@ -7022,17 +7546,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.4083</v>
+        <v>0.3339</v>
       </c>
       <c r="D19" t="n">
-        <v>0.097</v>
+        <v>0.1051</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -7041,22 +7565,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.4006</v>
+        <v>0.4083</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1046</v>
+        <v>0.097</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
@@ -7065,19 +7589,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.2526</v>
+        <v>0.428</v>
       </c>
       <c r="D21" t="n">
-        <v>0.077</v>
+        <v>0.0675</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
@@ -7094,14 +7618,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.2244</v>
+        <v>0.4006</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0706</v>
+        <v>0.1046</v>
       </c>
       <c r="E22" t="n">
         <v>9</v>
@@ -7118,17 +7642,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1958</v>
+        <v>0.2526</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0576</v>
+        <v>0.077</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
@@ -7142,17 +7666,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.2705</v>
+        <v>0.2244</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0493</v>
+        <v>0.0706</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
@@ -7166,14 +7690,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1075</v>
+        <v>0.1958</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0119</v>
+        <v>0.0576</v>
       </c>
       <c r="E25" t="n">
         <v>9</v>
@@ -7190,17 +7714,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.5113</v>
+        <v>0.2705</v>
       </c>
       <c r="D26" t="n">
         <v>0.0493</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
@@ -7214,17 +7738,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.3226</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0121</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
         <v>10</v>
@@ -7238,17 +7762,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.4684</v>
+        <v>0.5113</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1115</v>
+        <v>0.0493</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
@@ -7257,22 +7781,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.349</v>
+        <v>0.3226</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0883</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
         <v>10</v>
@@ -7281,19 +7805,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.2267</v>
+        <v>0.4684</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0717</v>
+        <v>0.1115</v>
       </c>
       <c r="E30" t="n">
         <v>9</v>
@@ -7305,22 +7829,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MIPROC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.2301</v>
+        <v>0.0388</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0728</v>
+        <v>0.0053</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
         <v>10</v>
@@ -7334,17 +7858,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2215</v>
+        <v>0.349</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0717</v>
+        <v>0.0883</v>
       </c>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
         <v>10</v>
@@ -7358,17 +7882,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1305</v>
+        <v>0.2267</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0282</v>
+        <v>0.0717</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F33" t="n">
         <v>10</v>
@@ -7382,14 +7906,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.125</v>
+        <v>0.2301</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0141</v>
+        <v>0.0728</v>
       </c>
       <c r="E34" t="n">
         <v>10</v>
@@ -7406,17 +7930,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.2471</v>
+        <v>0.2215</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0247</v>
+        <v>0.0717</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F35" t="n">
         <v>10</v>
@@ -7430,17 +7954,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.337</v>
+        <v>0.1305</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1005</v>
+        <v>0.0282</v>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
         <v>10</v>
@@ -7454,19 +7978,115 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MICI</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C40" t="n">
         <v>0.3283</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D40" t="n">
         <v>0.0762</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E40" t="n">
         <v>9</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7503,7 +8123,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.4</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="3">
@@ -7513,7 +8133,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.4</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="4">
@@ -7523,7 +8143,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.1</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="5">
@@ -7533,7 +8153,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
     </row>
   </sheetData>

--- a/Exp3_PTO_GRPO/eda/results/arms/stats/tables/claude-haiku-4-5/stats.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/stats/tables/claude-haiku-4-5/stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,7 +697,7 @@
         <v>0.007900000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0009</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         <v>0.008800000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0018</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="7">
@@ -801,7 +801,7 @@
         <v>0.0011</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1015</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="8">
@@ -905,7 +905,7 @@
         <v>0.002</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0329</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="10">
@@ -963,12 +963,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -977,39 +977,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.241</v>
+        <v>1.834</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.064</v>
+        <v>1.038</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.107</v>
+        <v>1.539</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3656</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.183</v>
+        <v>0.909</v>
       </c>
       <c r="K11" t="n">
-        <v>0.056</v>
+        <v>1.177</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.028</v>
+        <v>0.383</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0027</v>
+        <v>0.101</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.834</v>
+        <v>2.165</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.038</v>
+        <v>0.793</v>
       </c>
       <c r="G12" t="n">
-        <v>1.539</v>
+        <v>1.304</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.909</v>
+        <v>0.676</v>
       </c>
       <c r="K12" t="n">
-        <v>1.177</v>
+        <v>0.911</v>
       </c>
       <c r="L12" t="n">
-        <v>0.383</v>
+        <v>0.239</v>
       </c>
       <c r="M12" t="n">
-        <v>0.101</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.165</v>
+        <v>2.091</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0.793</v>
+        <v>0.844</v>
       </c>
       <c r="G13" t="n">
-        <v>1.304</v>
+        <v>1.43</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.676</v>
+        <v>0.73</v>
       </c>
       <c r="K13" t="n">
-        <v>0.911</v>
+        <v>0.964</v>
       </c>
       <c r="L13" t="n">
-        <v>0.239</v>
+        <v>0.246</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0786</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1133,16 +1133,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.091</v>
+        <v>2.439</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>0.844</v>
+        <v>0.889</v>
       </c>
       <c r="G14" t="n">
-        <v>1.43</v>
+        <v>1.234</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.73</v>
+        <v>0.753</v>
       </c>
       <c r="K14" t="n">
-        <v>0.964</v>
+        <v>1.03</v>
       </c>
       <c r="L14" t="n">
-        <v>0.246</v>
+        <v>0.263</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0786</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.439</v>
+        <v>1.831</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>0.889</v>
+        <v>0.544</v>
       </c>
       <c r="G15" t="n">
-        <v>1.234</v>
+        <v>0.881</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1205,16 +1205,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.753</v>
+        <v>0.417</v>
       </c>
       <c r="K15" t="n">
-        <v>1.03</v>
+        <v>0.667</v>
       </c>
       <c r="L15" t="n">
-        <v>0.263</v>
+        <v>0.204</v>
       </c>
       <c r="M15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0493</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1237,16 +1237,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.831</v>
+        <v>0.477</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>0.544</v>
+        <v>0.26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.881</v>
+        <v>0.873</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1257,16 +1257,16 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.417</v>
+        <v>0.202</v>
       </c>
       <c r="K16" t="n">
-        <v>0.667</v>
+        <v>0.318</v>
       </c>
       <c r="L16" t="n">
-        <v>0.204</v>
+        <v>0.193</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0493</v>
+        <v>0.0252</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.477</v>
+        <v>0.326</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>0.26</v>
+        <v>0.301</v>
       </c>
       <c r="G17" t="n">
-        <v>0.873</v>
+        <v>0.845</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1309,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.202</v>
+        <v>0.233</v>
       </c>
       <c r="K17" t="n">
-        <v>0.318</v>
+        <v>0.372</v>
       </c>
       <c r="L17" t="n">
-        <v>0.193</v>
+        <v>0.322</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0252</v>
+        <v>0.0276</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.326</v>
+        <v>1.681</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>0.301</v>
+        <v>1.05</v>
       </c>
       <c r="G18" t="n">
-        <v>0.845</v>
+        <v>1.228</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1361,16 +1361,16 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.233</v>
+        <v>0.887</v>
       </c>
       <c r="K18" t="n">
-        <v>0.372</v>
+        <v>1.221</v>
       </c>
       <c r="L18" t="n">
-        <v>0.322</v>
+        <v>0.334</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0276</v>
+        <v>0.1051</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.681</v>
+        <v>1.988</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.05</v>
+        <v>1.027</v>
       </c>
       <c r="G19" t="n">
-        <v>1.228</v>
+        <v>1.594</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1413,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.887</v>
+        <v>0.896</v>
       </c>
       <c r="K19" t="n">
-        <v>1.221</v>
+        <v>1.158</v>
       </c>
       <c r="L19" t="n">
-        <v>0.334</v>
+        <v>0.408</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1051</v>
+        <v>0.097</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1431,12 +1431,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.988</v>
+        <v>1.83</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>1.027</v>
+        <v>1.036</v>
       </c>
       <c r="G20" t="n">
-        <v>1.594</v>
+        <v>1.653</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1465,16 +1465,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.896</v>
+        <v>0.912</v>
       </c>
       <c r="K20" t="n">
-        <v>1.158</v>
+        <v>1.157</v>
       </c>
       <c r="L20" t="n">
-        <v>0.408</v>
+        <v>0.401</v>
       </c>
       <c r="M20" t="n">
-        <v>0.097</v>
+        <v>0.1046</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1483,12 +1483,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.198</v>
+        <v>2.117</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>0.605</v>
+        <v>0.838</v>
       </c>
       <c r="G21" t="n">
-        <v>1.106</v>
+        <v>1.177</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1517,16 +1517,16 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.49</v>
+        <v>0.694</v>
       </c>
       <c r="K21" t="n">
-        <v>0.707</v>
+        <v>0.983</v>
       </c>
       <c r="L21" t="n">
-        <v>0.428</v>
+        <v>0.253</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0675</v>
+        <v>0.077</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1549,16 +1549,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.83</v>
+        <v>2.042</v>
       </c>
       <c r="E22" t="n">
         <v>10</v>
       </c>
       <c r="F22" t="n">
-        <v>1.036</v>
+        <v>0.767</v>
       </c>
       <c r="G22" t="n">
-        <v>1.653</v>
+        <v>1.287</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1569,16 +1569,16 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.912</v>
+        <v>0.65</v>
       </c>
       <c r="K22" t="n">
-        <v>1.157</v>
+        <v>0.885</v>
       </c>
       <c r="L22" t="n">
-        <v>0.401</v>
+        <v>0.224</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1046</v>
+        <v>0.0706</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.117</v>
+        <v>2.464</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>0.838</v>
+        <v>0.609</v>
       </c>
       <c r="G23" t="n">
-        <v>1.177</v>
+        <v>0.899</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1621,16 +1621,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.694</v>
+        <v>0.479</v>
       </c>
       <c r="K23" t="n">
-        <v>0.983</v>
+        <v>0.747</v>
       </c>
       <c r="L23" t="n">
-        <v>0.253</v>
+        <v>0.196</v>
       </c>
       <c r="M23" t="n">
-        <v>0.077</v>
+        <v>0.0576</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.042</v>
+        <v>1.839</v>
       </c>
       <c r="E24" t="n">
         <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>0.767</v>
+        <v>0.513</v>
       </c>
       <c r="G24" t="n">
-        <v>1.287</v>
+        <v>0.88</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1673,16 +1673,16 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.65</v>
+        <v>0.393</v>
       </c>
       <c r="K24" t="n">
-        <v>0.885</v>
+        <v>0.62</v>
       </c>
       <c r="L24" t="n">
-        <v>0.224</v>
+        <v>0.271</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0706</v>
+        <v>0.0493</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1705,39 +1705,39 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.464</v>
+        <v>0.502</v>
       </c>
       <c r="E25" t="n">
         <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>0.609</v>
+        <v>0.111</v>
       </c>
       <c r="G25" t="n">
-        <v>0.899</v>
+        <v>0.426</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J25" t="n">
-        <v>0.479</v>
+        <v>0.059</v>
       </c>
       <c r="K25" t="n">
-        <v>0.747</v>
+        <v>0.164</v>
       </c>
       <c r="L25" t="n">
-        <v>0.196</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0576</v>
+        <v>0.0121</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="26">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1757,16 +1757,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.839</v>
+        <v>0.364</v>
       </c>
       <c r="E26" t="n">
         <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>0.513</v>
+        <v>0.461</v>
       </c>
       <c r="G26" t="n">
-        <v>0.88</v>
+        <v>0.992</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1777,13 +1777,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.393</v>
+        <v>0.365</v>
       </c>
       <c r="K26" t="n">
-        <v>0.62</v>
+        <v>0.553</v>
       </c>
       <c r="L26" t="n">
-        <v>0.271</v>
+        <v>0.511</v>
       </c>
       <c r="M26" t="n">
         <v>0.0493</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1809,39 +1809,39 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.502</v>
+        <v>1.673</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.111</v>
+        <v>0.967</v>
       </c>
       <c r="G27" t="n">
-        <v>0.426</v>
+        <v>1.335</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.059</v>
+        <v>0.823</v>
       </c>
       <c r="K27" t="n">
-        <v>0.164</v>
+        <v>1.104</v>
       </c>
       <c r="L27" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.323</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0121</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1861,16 +1861,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.364</v>
+        <v>1.987</v>
       </c>
       <c r="E28" t="n">
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>0.461</v>
+        <v>1.106</v>
       </c>
       <c r="G28" t="n">
-        <v>0.992</v>
+        <v>1.718</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.365</v>
+        <v>0.98</v>
       </c>
       <c r="K28" t="n">
-        <v>0.553</v>
+        <v>1.239</v>
       </c>
       <c r="L28" t="n">
-        <v>0.511</v>
+        <v>0.468</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0493</v>
+        <v>0.1115</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -1899,12 +1899,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.673</v>
+        <v>1.834</v>
       </c>
       <c r="E29" t="n">
         <v>10</v>
       </c>
       <c r="F29" t="n">
-        <v>0.967</v>
+        <v>0.833</v>
       </c>
       <c r="G29" t="n">
-        <v>1.335</v>
+        <v>1.124</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1933,16 +1933,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.823</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>1.104</v>
+        <v>0.981</v>
       </c>
       <c r="L29" t="n">
-        <v>0.323</v>
+        <v>0.349</v>
       </c>
       <c r="M29" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0883</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -1951,12 +1951,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.987</v>
+        <v>2.149</v>
       </c>
       <c r="E30" t="n">
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>1.106</v>
+        <v>0.701</v>
       </c>
       <c r="G30" t="n">
-        <v>1.718</v>
+        <v>0.973</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1985,16 +1985,16 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.98</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>1.239</v>
+        <v>0.844</v>
       </c>
       <c r="L30" t="n">
-        <v>0.468</v>
+        <v>0.227</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1115</v>
+        <v>0.0717</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2003,12 +2003,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2017,39 +2017,39 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.208</v>
+        <v>2.099</v>
       </c>
       <c r="E31" t="n">
         <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>0.057</v>
+        <v>0.708</v>
       </c>
       <c r="G31" t="n">
-        <v>0.102</v>
+        <v>0.957</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3535</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.059</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.165</v>
+        <v>0.853</v>
       </c>
       <c r="L31" t="n">
-        <v>0.039</v>
+        <v>0.23</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0053</v>
+        <v>0.0728</v>
       </c>
       <c r="N31" t="n">
-        <v>0.3535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.834</v>
+        <v>2.464</v>
       </c>
       <c r="E32" t="n">
         <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>0.833</v>
+        <v>0.72</v>
       </c>
       <c r="G32" t="n">
-        <v>1.124</v>
+        <v>1.055</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="K32" t="n">
-        <v>0.981</v>
+        <v>0.859</v>
       </c>
       <c r="L32" t="n">
-        <v>0.349</v>
+        <v>0.222</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0883</v>
+        <v>0.0717</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2121,36 +2121,36 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.149</v>
+        <v>1.852</v>
       </c>
       <c r="E33" t="n">
         <v>10</v>
       </c>
       <c r="F33" t="n">
-        <v>0.701</v>
+        <v>0.297</v>
       </c>
       <c r="G33" t="n">
-        <v>0.973</v>
+        <v>0.52</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.177</v>
       </c>
       <c r="K33" t="n">
-        <v>0.844</v>
+        <v>0.409</v>
       </c>
       <c r="L33" t="n">
-        <v>0.227</v>
+        <v>0.131</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0717</v>
+        <v>0.0282</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2173,36 +2173,36 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.099</v>
+        <v>0.509</v>
       </c>
       <c r="E34" t="n">
         <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>0.708</v>
+        <v>0.178</v>
       </c>
       <c r="G34" t="n">
-        <v>0.957</v>
+        <v>0.626</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.121</v>
       </c>
       <c r="K34" t="n">
-        <v>0.853</v>
+        <v>0.236</v>
       </c>
       <c r="L34" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0728</v>
+        <v>0.0149</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2225,36 +2225,36 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2.464</v>
+        <v>0.37</v>
       </c>
       <c r="E35" t="n">
         <v>10</v>
       </c>
       <c r="F35" t="n">
-        <v>0.72</v>
+        <v>0.21</v>
       </c>
       <c r="G35" t="n">
-        <v>1.055</v>
+        <v>0.48</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.583</v>
+        <v>0.125</v>
       </c>
       <c r="K35" t="n">
-        <v>0.859</v>
+        <v>0.296</v>
       </c>
       <c r="L35" t="n">
-        <v>0.222</v>
+        <v>0.247</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0717</v>
+        <v>0.0247</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2277,36 +2277,36 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.852</v>
+        <v>1.683</v>
       </c>
       <c r="E36" t="n">
         <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>0.297</v>
+        <v>0.921</v>
       </c>
       <c r="G36" t="n">
-        <v>0.52</v>
+        <v>1.043</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.177</v>
+        <v>0.75</v>
       </c>
       <c r="K36" t="n">
-        <v>0.409</v>
+        <v>1.094</v>
       </c>
       <c r="L36" t="n">
-        <v>0.131</v>
+        <v>0.337</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0282</v>
+        <v>0.1005</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2329,36 +2329,36 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.509</v>
+        <v>1.984</v>
       </c>
       <c r="E37" t="n">
         <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>0.178</v>
+        <v>0.746</v>
       </c>
       <c r="G37" t="n">
-        <v>0.626</v>
+        <v>1.039</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.121</v>
+        <v>0.607</v>
       </c>
       <c r="K37" t="n">
-        <v>0.236</v>
+        <v>0.887</v>
       </c>
       <c r="L37" t="n">
-        <v>0.11</v>
+        <v>0.328</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0149</v>
+        <v>0.0762</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -2367,50 +2367,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>final</t>
+          <t>best</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.37</v>
+        <v>1.861</v>
       </c>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>0.21</v>
+        <v>0.776</v>
       </c>
       <c r="G38" t="n">
-        <v>0.48</v>
+        <v>1.459</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.125</v>
+        <v>0.671</v>
       </c>
       <c r="K38" t="n">
-        <v>0.296</v>
+        <v>0.88</v>
       </c>
       <c r="L38" t="n">
-        <v>0.247</v>
+        <v>0.103</v>
       </c>
       <c r="M38" t="n">
-        <v>0.0247</v>
+        <v>0.0264</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -2419,30 +2419,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>final</t>
+          <t>best</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.683</v>
+        <v>2.222</v>
       </c>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>0.921</v>
+        <v>0.635</v>
       </c>
       <c r="G39" t="n">
-        <v>1.043</v>
+        <v>1.082</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2453,16 +2453,16 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.75</v>
+        <v>0.518</v>
       </c>
       <c r="K39" t="n">
-        <v>1.094</v>
+        <v>0.752</v>
       </c>
       <c r="L39" t="n">
-        <v>0.337</v>
+        <v>0.109</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1005</v>
+        <v>0.0295</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -2471,30 +2471,30 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>final</t>
+          <t>best</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1.984</v>
+        <v>2.087</v>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>0.746</v>
+        <v>0.612</v>
       </c>
       <c r="G40" t="n">
-        <v>1.039</v>
+        <v>1.011</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2505,16 +2505,16 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.607</v>
+        <v>0.49</v>
       </c>
       <c r="K40" t="n">
-        <v>0.887</v>
+        <v>0.727</v>
       </c>
       <c r="L40" t="n">
-        <v>0.328</v>
+        <v>0.058</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0762</v>
+        <v>0.0224</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2523,53 +2523,53 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>final</t>
+          <t>best</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.189</v>
+        <v>2.521</v>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>0.254</v>
+        <v>0.46</v>
       </c>
       <c r="G41" t="n">
-        <v>0.391</v>
+        <v>0.677</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.125</v>
+        <v>0.326</v>
       </c>
       <c r="K41" t="n">
-        <v>0.379</v>
+        <v>0.595</v>
       </c>
       <c r="L41" t="n">
-        <v>0.135</v>
+        <v>0.036</v>
       </c>
       <c r="M41" t="n">
-        <v>0.019</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2589,16 +2589,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.861</v>
+        <v>1.888</v>
       </c>
       <c r="E42" t="n">
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>0.776</v>
+        <v>0.495</v>
       </c>
       <c r="G42" t="n">
-        <v>1.459</v>
+        <v>0.894</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2609,16 +2609,16 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.671</v>
+        <v>0.388</v>
       </c>
       <c r="K42" t="n">
-        <v>0.88</v>
+        <v>0.599</v>
       </c>
       <c r="L42" t="n">
-        <v>0.103</v>
+        <v>0.033</v>
       </c>
       <c r="M42" t="n">
-        <v>0.0264</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2641,39 +2641,39 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.222</v>
+        <v>0.523</v>
       </c>
       <c r="E43" t="n">
         <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>0.635</v>
+        <v>0.081</v>
       </c>
       <c r="G43" t="n">
-        <v>1.082</v>
+        <v>0.325</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="J43" t="n">
-        <v>0.518</v>
+        <v>0.032</v>
       </c>
       <c r="K43" t="n">
-        <v>0.752</v>
+        <v>0.133</v>
       </c>
       <c r="L43" t="n">
-        <v>0.109</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0295</v>
+        <v>0.0011</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="44">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2693,39 +2693,39 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.087</v>
+        <v>0.384</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
       </c>
       <c r="F44" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="L44" t="n">
         <v>0.612</v>
       </c>
-      <c r="G44" t="n">
-        <v>1.011</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.058</v>
-      </c>
       <c r="M44" t="n">
-        <v>0.0224</v>
+        <v>0.0635</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.4946</v>
       </c>
     </row>
     <row r="45">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2745,36 +2745,36 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.521</v>
+        <v>1.694</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>0.46</v>
+        <v>0.883</v>
       </c>
       <c r="G45" t="n">
-        <v>0.677</v>
+        <v>1.268</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.326</v>
+        <v>0.746</v>
       </c>
       <c r="K45" t="n">
-        <v>0.595</v>
+        <v>1.021</v>
       </c>
       <c r="L45" t="n">
-        <v>0.036</v>
+        <v>0.005</v>
       </c>
       <c r="M45" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2797,16 +2797,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.888</v>
+        <v>2.028</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>0.495</v>
+        <v>0.668</v>
       </c>
       <c r="G46" t="n">
-        <v>0.894</v>
+        <v>1.273</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2817,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.388</v>
+        <v>0.572</v>
       </c>
       <c r="K46" t="n">
-        <v>0.599</v>
+        <v>0.772</v>
       </c>
       <c r="L46" t="n">
-        <v>0.033</v>
+        <v>0.202</v>
       </c>
       <c r="M46" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0508</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -2835,12 +2835,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2849,50 +2849,50 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.523</v>
+        <v>1.834</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F47" t="n">
-        <v>0.081</v>
+        <v>1.078</v>
       </c>
       <c r="G47" t="n">
-        <v>0.325</v>
+        <v>1.466</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.0038</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.032</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>0.133</v>
+        <v>1.228</v>
       </c>
       <c r="L47" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.383</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0011</v>
+        <v>0.101</v>
       </c>
       <c r="N47" t="n">
-        <v>0.0115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2901,50 +2901,50 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.384</v>
+        <v>2.165</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
-        <v>0.024</v>
+        <v>0.723</v>
       </c>
       <c r="G48" t="n">
-        <v>0.06900000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4946</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.043</v>
+        <v>0.603</v>
       </c>
       <c r="K48" t="n">
-        <v>0.092</v>
+        <v>0.852</v>
       </c>
       <c r="L48" t="n">
-        <v>0.612</v>
+        <v>0.239</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0635</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>0.8385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1.694</v>
+        <v>2.091</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
-        <v>0.883</v>
+        <v>0.701</v>
       </c>
       <c r="G49" t="n">
-        <v>1.268</v>
+        <v>1.004</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2973,16 +2973,16 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.746</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>1.021</v>
+        <v>0.839</v>
       </c>
       <c r="L49" t="n">
-        <v>0.005</v>
+        <v>0.246</v>
       </c>
       <c r="M49" t="n">
-        <v>0.002</v>
+        <v>0.0786</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -2991,12 +2991,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3005,16 +3005,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.028</v>
+        <v>2.439</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F50" t="n">
-        <v>0.668</v>
+        <v>0.766</v>
       </c>
       <c r="G50" t="n">
-        <v>1.273</v>
+        <v>1.041</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3025,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.572</v>
+        <v>0.623</v>
       </c>
       <c r="K50" t="n">
-        <v>0.772</v>
+        <v>0.917</v>
       </c>
       <c r="L50" t="n">
-        <v>0.202</v>
+        <v>0.263</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0508</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3043,12 +3043,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3057,39 +3057,39 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.241</v>
+        <v>1.831</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F51" t="n">
-        <v>0.044</v>
+        <v>0.552</v>
       </c>
       <c r="G51" t="n">
-        <v>0.07199999999999999</v>
+        <v>1.013</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4192</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.443</v>
       </c>
       <c r="K51" t="n">
-        <v>0.164</v>
+        <v>0.659</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.028</v>
+        <v>0.204</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0027</v>
+        <v>0.0493</v>
       </c>
       <c r="N51" t="n">
-        <v>0.8385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3109,36 +3109,36 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1.834</v>
+        <v>0.477</v>
       </c>
       <c r="E52" t="n">
         <v>7</v>
       </c>
       <c r="F52" t="n">
-        <v>1.078</v>
+        <v>0.199</v>
       </c>
       <c r="G52" t="n">
-        <v>1.466</v>
+        <v>0.754</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.148</v>
       </c>
       <c r="K52" t="n">
-        <v>1.228</v>
+        <v>0.251</v>
       </c>
       <c r="L52" t="n">
-        <v>0.383</v>
+        <v>0.193</v>
       </c>
       <c r="M52" t="n">
-        <v>0.101</v>
+        <v>0.0252</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3161,36 +3161,36 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2.165</v>
+        <v>0.326</v>
       </c>
       <c r="E53" t="n">
         <v>7</v>
       </c>
       <c r="F53" t="n">
-        <v>0.723</v>
+        <v>0.253</v>
       </c>
       <c r="G53" t="n">
-        <v>1.17</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.603</v>
+        <v>0.183</v>
       </c>
       <c r="K53" t="n">
-        <v>0.852</v>
+        <v>0.329</v>
       </c>
       <c r="L53" t="n">
-        <v>0.239</v>
+        <v>0.322</v>
       </c>
       <c r="M53" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0276</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3213,16 +3213,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.091</v>
+        <v>1.681</v>
       </c>
       <c r="E54" t="n">
         <v>7</v>
       </c>
       <c r="F54" t="n">
-        <v>0.701</v>
+        <v>1.188</v>
       </c>
       <c r="G54" t="n">
-        <v>1.004</v>
+        <v>1.403</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3233,16 +3233,16 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5659999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="K54" t="n">
-        <v>0.839</v>
+        <v>1.362</v>
       </c>
       <c r="L54" t="n">
-        <v>0.246</v>
+        <v>0.334</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0786</v>
+        <v>0.1051</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3265,16 +3265,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.439</v>
+        <v>1.988</v>
       </c>
       <c r="E55" t="n">
         <v>7</v>
       </c>
       <c r="F55" t="n">
-        <v>0.766</v>
+        <v>0.968</v>
       </c>
       <c r="G55" t="n">
-        <v>1.041</v>
+        <v>1.338</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3285,16 +3285,16 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.623</v>
+        <v>0.822</v>
       </c>
       <c r="K55" t="n">
-        <v>0.917</v>
+        <v>1.112</v>
       </c>
       <c r="L55" t="n">
-        <v>0.263</v>
+        <v>0.408</v>
       </c>
       <c r="M55" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -3303,12 +3303,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3317,16 +3317,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1.831</v>
+        <v>1.83</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.552</v>
+        <v>1.091</v>
       </c>
       <c r="G56" t="n">
-        <v>1.013</v>
+        <v>1.621</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3337,16 +3337,16 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.443</v>
+        <v>0.962</v>
       </c>
       <c r="K56" t="n">
-        <v>0.659</v>
+        <v>1.225</v>
       </c>
       <c r="L56" t="n">
-        <v>0.204</v>
+        <v>0.401</v>
       </c>
       <c r="M56" t="n">
-        <v>0.0493</v>
+        <v>0.1046</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -3355,12 +3355,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3369,36 +3369,36 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.477</v>
+        <v>2.117</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
-        <v>0.199</v>
+        <v>0.827</v>
       </c>
       <c r="G57" t="n">
-        <v>0.754</v>
+        <v>1.15</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0.148</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>0.251</v>
+        <v>0.974</v>
       </c>
       <c r="L57" t="n">
-        <v>0.193</v>
+        <v>0.253</v>
       </c>
       <c r="M57" t="n">
-        <v>0.0252</v>
+        <v>0.077</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -3407,12 +3407,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3421,36 +3421,36 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.326</v>
+        <v>2.042</v>
       </c>
       <c r="E58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>0.253</v>
+        <v>0.806</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6840000000000001</v>
+        <v>1.316</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.183</v>
+        <v>0.68</v>
       </c>
       <c r="K58" t="n">
-        <v>0.329</v>
+        <v>0.925</v>
       </c>
       <c r="L58" t="n">
-        <v>0.322</v>
+        <v>0.224</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0276</v>
+        <v>0.0706</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -3459,12 +3459,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1.681</v>
+        <v>2.464</v>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F59" t="n">
-        <v>1.188</v>
+        <v>0.635</v>
       </c>
       <c r="G59" t="n">
-        <v>1.403</v>
+        <v>0.911</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3493,16 +3493,16 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>1.025</v>
+        <v>0.495</v>
       </c>
       <c r="K59" t="n">
-        <v>1.362</v>
+        <v>0.781</v>
       </c>
       <c r="L59" t="n">
-        <v>0.334</v>
+        <v>0.196</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1051</v>
+        <v>0.0576</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -3511,12 +3511,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3525,16 +3525,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.988</v>
+        <v>1.839</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F60" t="n">
-        <v>0.968</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>1.338</v>
+        <v>0.969</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3545,16 +3545,16 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.822</v>
+        <v>0.445</v>
       </c>
       <c r="K60" t="n">
-        <v>1.112</v>
+        <v>0.669</v>
       </c>
       <c r="L60" t="n">
-        <v>0.408</v>
+        <v>0.271</v>
       </c>
       <c r="M60" t="n">
-        <v>0.097</v>
+        <v>0.0493</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -3563,12 +3563,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3577,39 +3577,39 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.198</v>
+        <v>0.502</v>
       </c>
       <c r="E61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F61" t="n">
-        <v>0.427</v>
+        <v>0.122</v>
       </c>
       <c r="G61" t="n">
-        <v>0.659</v>
+        <v>0.453</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J61" t="n">
-        <v>0.294</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>0.551</v>
+        <v>0.177</v>
       </c>
       <c r="L61" t="n">
-        <v>0.428</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0675</v>
+        <v>0.0121</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="62">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3629,16 +3629,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.83</v>
+        <v>0.364</v>
       </c>
       <c r="E62" t="n">
         <v>9</v>
       </c>
       <c r="F62" t="n">
-        <v>1.091</v>
+        <v>0.382</v>
       </c>
       <c r="G62" t="n">
-        <v>1.621</v>
+        <v>0.895</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3649,16 +3649,16 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0.962</v>
+        <v>0.3</v>
       </c>
       <c r="K62" t="n">
-        <v>1.225</v>
+        <v>0.465</v>
       </c>
       <c r="L62" t="n">
-        <v>0.401</v>
+        <v>0.511</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1046</v>
+        <v>0.0493</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3681,16 +3681,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2.117</v>
+        <v>1.673</v>
       </c>
       <c r="E63" t="n">
         <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>0.827</v>
+        <v>1.048</v>
       </c>
       <c r="G63" t="n">
-        <v>1.15</v>
+        <v>1.257</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3701,16 +3701,16 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.885</v>
       </c>
       <c r="K63" t="n">
-        <v>0.974</v>
+        <v>1.215</v>
       </c>
       <c r="L63" t="n">
-        <v>0.253</v>
+        <v>0.323</v>
       </c>
       <c r="M63" t="n">
-        <v>0.077</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3733,16 +3733,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2.042</v>
+        <v>1.987</v>
       </c>
       <c r="E64" t="n">
         <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>0.806</v>
+        <v>1.135</v>
       </c>
       <c r="G64" t="n">
-        <v>1.316</v>
+        <v>1.827</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3753,16 +3753,16 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.68</v>
+        <v>1.015</v>
       </c>
       <c r="K64" t="n">
-        <v>0.925</v>
+        <v>1.259</v>
       </c>
       <c r="L64" t="n">
-        <v>0.224</v>
+        <v>0.468</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0706</v>
+        <v>0.1115</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -3771,12 +3771,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3785,16 +3785,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2.464</v>
+        <v>1.834</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F65" t="n">
-        <v>0.635</v>
+        <v>0.902</v>
       </c>
       <c r="G65" t="n">
-        <v>0.911</v>
+        <v>1.306</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3805,16 +3805,16 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.495</v>
+        <v>0.761</v>
       </c>
       <c r="K65" t="n">
-        <v>0.781</v>
+        <v>1.045</v>
       </c>
       <c r="L65" t="n">
-        <v>0.196</v>
+        <v>0.349</v>
       </c>
       <c r="M65" t="n">
-        <v>0.0576</v>
+        <v>0.0883</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -3823,12 +3823,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3837,16 +3837,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.839</v>
+        <v>2.149</v>
       </c>
       <c r="E66" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F66" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.659</v>
       </c>
       <c r="G66" t="n">
-        <v>0.969</v>
+        <v>0.866</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3857,16 +3857,16 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0.445</v>
+        <v>0.508</v>
       </c>
       <c r="K66" t="n">
-        <v>0.669</v>
+        <v>0.802</v>
       </c>
       <c r="L66" t="n">
-        <v>0.271</v>
+        <v>0.227</v>
       </c>
       <c r="M66" t="n">
-        <v>0.0493</v>
+        <v>0.0717</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -3875,12 +3875,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3889,50 +3889,50 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.502</v>
+        <v>2.099</v>
       </c>
       <c r="E67" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F67" t="n">
-        <v>0.122</v>
+        <v>0.674</v>
       </c>
       <c r="G67" t="n">
-        <v>0.453</v>
+        <v>0.868</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.517</v>
       </c>
       <c r="K67" t="n">
-        <v>0.177</v>
+        <v>0.826</v>
       </c>
       <c r="L67" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="M67" t="n">
-        <v>0.0121</v>
+        <v>0.0728</v>
       </c>
       <c r="N67" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3941,36 +3941,36 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.364</v>
+        <v>2.464</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F68" t="n">
-        <v>0.382</v>
+        <v>0.63</v>
       </c>
       <c r="G68" t="n">
-        <v>0.895</v>
+        <v>0.794</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0.3</v>
+        <v>0.47</v>
       </c>
       <c r="K68" t="n">
-        <v>0.465</v>
+        <v>0.783</v>
       </c>
       <c r="L68" t="n">
-        <v>0.511</v>
+        <v>0.222</v>
       </c>
       <c r="M68" t="n">
-        <v>0.0493</v>
+        <v>0.0717</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -3979,12 +3979,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3993,36 +3993,36 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.673</v>
+        <v>1.852</v>
       </c>
       <c r="E69" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F69" t="n">
-        <v>1.048</v>
+        <v>0.362</v>
       </c>
       <c r="G69" t="n">
-        <v>1.257</v>
+        <v>0.642</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0.885</v>
+        <v>0.253</v>
       </c>
       <c r="K69" t="n">
-        <v>1.215</v>
+        <v>0.474</v>
       </c>
       <c r="L69" t="n">
-        <v>0.323</v>
+        <v>0.131</v>
       </c>
       <c r="M69" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0282</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -4031,12 +4031,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4045,50 +4045,50 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1.987</v>
+        <v>0.509</v>
       </c>
       <c r="E70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F70" t="n">
-        <v>1.135</v>
+        <v>0.095</v>
       </c>
       <c r="G70" t="n">
-        <v>1.827</v>
+        <v>0.314</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>0.0031</v>
       </c>
       <c r="J70" t="n">
-        <v>1.015</v>
+        <v>0.037</v>
       </c>
       <c r="K70" t="n">
-        <v>1.259</v>
+        <v>0.159</v>
       </c>
       <c r="L70" t="n">
-        <v>0.468</v>
+        <v>0.11</v>
       </c>
       <c r="M70" t="n">
-        <v>0.1115</v>
+        <v>0.0149</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>0.0031</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4097,39 +4097,39 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.208</v>
+        <v>0.37</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>0.515</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.115</v>
+        <v>0.128</v>
       </c>
       <c r="K71" t="n">
-        <v>0.104</v>
+        <v>0.294</v>
       </c>
       <c r="L71" t="n">
-        <v>0.039</v>
+        <v>0.247</v>
       </c>
       <c r="M71" t="n">
-        <v>0.0053</v>
+        <v>0.0247</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4149,16 +4149,16 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.834</v>
+        <v>1.683</v>
       </c>
       <c r="E72" t="n">
         <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.902</v>
+        <v>1.025</v>
       </c>
       <c r="G72" t="n">
-        <v>1.306</v>
+        <v>1.164</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4169,16 +4169,16 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0.761</v>
+        <v>0.844</v>
       </c>
       <c r="K72" t="n">
-        <v>1.045</v>
+        <v>1.204</v>
       </c>
       <c r="L72" t="n">
-        <v>0.349</v>
+        <v>0.337</v>
       </c>
       <c r="M72" t="n">
-        <v>0.0883</v>
+        <v>0.1005</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4201,16 +4201,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.149</v>
+        <v>1.984</v>
       </c>
       <c r="E73" t="n">
         <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>0.659</v>
+        <v>0.778</v>
       </c>
       <c r="G73" t="n">
-        <v>0.866</v>
+        <v>1.194</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4221,435 +4221,19 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0.508</v>
+        <v>0.651</v>
       </c>
       <c r="K73" t="n">
-        <v>0.802</v>
+        <v>0.912</v>
       </c>
       <c r="L73" t="n">
-        <v>0.227</v>
+        <v>0.328</v>
       </c>
       <c r="M73" t="n">
-        <v>0.0717</v>
+        <v>0.0762</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>CSQ-8</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2.099</v>
-      </c>
-      <c r="E74" t="n">
-        <v>7</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0.0728</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>MI-SAT</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>2.464</v>
-      </c>
-      <c r="E75" t="n">
-        <v>7</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0.0717</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>MITI</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>1.852</v>
-      </c>
-      <c r="E76" t="n">
-        <v>7</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0.0282</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>PCT</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="E77" t="n">
-        <v>7</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0.0149</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0.0061</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>MICI</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E78" t="n">
-        <v>7</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>1.683</v>
-      </c>
-      <c r="E79" t="n">
-        <v>7</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1.025</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1.164</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1.204</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0.1005</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>1.984</v>
-      </c>
-      <c r="E80" t="n">
-        <v>7</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1.194</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.651</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0.912</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0.0762</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="E81" t="n">
-        <v>7</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="J81" t="n">
-        <v>-0.044</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0.1576</v>
       </c>
     </row>
   </sheetData>
@@ -4663,7 +4247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4949,22 +4533,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.956099999999999</v>
+        <v>368.6102</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5363</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.384</v>
       </c>
       <c r="F11" t="n">
         <v>11</v>
@@ -4981,17 +4565,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>368.6102</v>
+        <v>277.0336</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.384</v>
+        <v>0.2886</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
@@ -5008,17 +4592,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>277.0336</v>
+        <v>282.3218</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2886</v>
+        <v>0.2941</v>
       </c>
       <c r="F13" t="n">
         <v>11</v>
@@ -5035,17 +4619,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>282.3218</v>
+        <v>304.035</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2941</v>
+        <v>0.3167</v>
       </c>
       <c r="F14" t="n">
         <v>11</v>
@@ -5062,17 +4646,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>304.035</v>
+        <v>135.0381</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3167</v>
+        <v>0.1407</v>
       </c>
       <c r="F15" t="n">
         <v>11</v>
@@ -5089,23 +4673,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>135.0381</v>
+        <v>171.6621</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1407</v>
+        <v>0.1807</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
@@ -5116,23 +4700,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>171.6621</v>
+        <v>151.4486</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1807</v>
+        <v>0.1578</v>
       </c>
       <c r="F17" t="n">
         <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
@@ -5143,17 +4727,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>151.4486</v>
+        <v>335.3761</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1578</v>
+        <v>0.3494</v>
       </c>
       <c r="F18" t="n">
         <v>11</v>
@@ -5170,17 +4754,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>335.3761</v>
+        <v>351.3549</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3494</v>
+        <v>0.366</v>
       </c>
       <c r="F19" t="n">
         <v>11</v>
@@ -5192,22 +4776,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>351.3549</v>
+        <v>377.8588</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.366</v>
+        <v>0.3936</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
@@ -5219,22 +4803,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>227.3061</v>
+        <v>263.2663</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2368</v>
+        <v>0.2742</v>
       </c>
       <c r="F21" t="n">
         <v>11</v>
@@ -5251,17 +4835,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>377.8588</v>
+        <v>228.99</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3936</v>
+        <v>0.2385</v>
       </c>
       <c r="F22" t="n">
         <v>11</v>
@@ -5278,17 +4862,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>263.2663</v>
+        <v>191.3091</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2742</v>
+        <v>0.1993</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
@@ -5305,17 +4889,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>228.99</v>
+        <v>193.15</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2385</v>
+        <v>0.2012</v>
       </c>
       <c r="F24" t="n">
         <v>11</v>
@@ -5332,23 +4916,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>191.3091</v>
+        <v>31.0736</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1993</v>
+        <v>0.0366</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
@@ -5359,17 +4943,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>193.15</v>
+        <v>273.176</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2012</v>
+        <v>0.2846</v>
       </c>
       <c r="F26" t="n">
         <v>11</v>
@@ -5386,23 +4970,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31.0736</v>
+        <v>282.9041</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0366</v>
+        <v>0.2947</v>
       </c>
       <c r="F27" t="n">
         <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28">
@@ -5413,17 +4997,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>273.176</v>
+        <v>436.8634</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2846</v>
+        <v>0.4551</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
@@ -5435,22 +5019,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>282.9041</v>
+        <v>256.2686</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2947</v>
+        <v>0.2669</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
@@ -5462,22 +5046,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>436.8634</v>
+        <v>209.1506</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4551</v>
+        <v>0.2179</v>
       </c>
       <c r="F30" t="n">
         <v>11</v>
@@ -5489,22 +5073,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>23.1168</v>
+        <v>199.1087</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0103</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0241</v>
+        <v>0.2074</v>
       </c>
       <c r="F31" t="n">
         <v>11</v>
@@ -5521,17 +5105,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>256.2686</v>
+        <v>197.6735</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2669</v>
+        <v>0.2059</v>
       </c>
       <c r="F32" t="n">
         <v>11</v>
@@ -5548,17 +5132,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>209.1506</v>
+        <v>76.4301</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2179</v>
+        <v>0.0796</v>
       </c>
       <c r="F33" t="n">
         <v>11</v>
@@ -5575,23 +5159,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>199.1087</v>
+        <v>74.9162</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2074</v>
+        <v>0.0892</v>
       </c>
       <c r="F34" t="n">
         <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
@@ -5602,17 +5186,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>197.6735</v>
+        <v>83.9836</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2059</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="F35" t="n">
         <v>11</v>
@@ -5629,17 +5213,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>76.4301</v>
+        <v>252.6374</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0796</v>
+        <v>0.2632</v>
       </c>
       <c r="F36" t="n">
         <v>11</v>
@@ -5656,131 +5240,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>74.9162</v>
+        <v>220.7438</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0892</v>
+        <v>0.2299</v>
       </c>
       <c r="F37" t="n">
         <v>11</v>
       </c>
       <c r="G37" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>MICI</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>83.9836</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.08749999999999999</v>
-      </c>
-      <c r="F38" t="n">
-        <v>11</v>
-      </c>
-      <c r="G38" t="n">
         <v>96</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>252.6374</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.2632</v>
-      </c>
-      <c r="F39" t="n">
-        <v>11</v>
-      </c>
-      <c r="G39" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>220.7438</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.2299</v>
-      </c>
-      <c r="F40" t="n">
-        <v>11</v>
-      </c>
-      <c r="G40" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>27.8583</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.0293</v>
-      </c>
-      <c r="F41" t="n">
-        <v>11</v>
-      </c>
-      <c r="G41" t="n">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -7095,7 +6571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7349,22 +6825,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.0282</v>
+        <v>0.3833</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0027</v>
+        <v>0.101</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -7378,17 +6854,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.3833</v>
+        <v>0.2386</v>
       </c>
       <c r="D12" t="n">
-        <v>0.101</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
@@ -7402,17 +6878,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2386</v>
+        <v>0.2459</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0786</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
@@ -7426,17 +6902,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2459</v>
+        <v>0.263</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0786</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -7450,14 +6926,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.263</v>
+        <v>0.2043</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0493</v>
       </c>
       <c r="E15" t="n">
         <v>9</v>
@@ -7474,14 +6950,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2043</v>
+        <v>0.1933</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0493</v>
+        <v>0.0252</v>
       </c>
       <c r="E16" t="n">
         <v>9</v>
@@ -7498,17 +6974,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.1933</v>
+        <v>0.3216</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0252</v>
+        <v>0.0276</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
@@ -7522,17 +6998,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.3216</v>
+        <v>0.3339</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0276</v>
+        <v>0.1051</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
@@ -7546,17 +7022,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.3339</v>
+        <v>0.4083</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1051</v>
+        <v>0.097</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -7565,22 +7041,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.4083</v>
+        <v>0.4006</v>
       </c>
       <c r="D20" t="n">
-        <v>0.097</v>
+        <v>0.1046</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
@@ -7589,19 +7065,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.428</v>
+        <v>0.2526</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0675</v>
+        <v>0.077</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
@@ -7618,14 +7094,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.4006</v>
+        <v>0.2244</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1046</v>
+        <v>0.0706</v>
       </c>
       <c r="E22" t="n">
         <v>9</v>
@@ -7642,17 +7118,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.2526</v>
+        <v>0.1958</v>
       </c>
       <c r="D23" t="n">
-        <v>0.077</v>
+        <v>0.0576</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
@@ -7666,17 +7142,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.2244</v>
+        <v>0.2705</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0706</v>
+        <v>0.0493</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
@@ -7690,14 +7166,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1958</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0576</v>
+        <v>0.0121</v>
       </c>
       <c r="E25" t="n">
         <v>9</v>
@@ -7714,17 +7190,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.2705</v>
+        <v>0.5113</v>
       </c>
       <c r="D26" t="n">
         <v>0.0493</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
@@ -7738,17 +7214,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.3226</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0121</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
         <v>10</v>
@@ -7762,17 +7238,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MICI</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.5113</v>
+        <v>0.4684</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0493</v>
+        <v>0.1115</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
@@ -7781,22 +7257,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q1Q2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.3226</v>
+        <v>0.349</v>
       </c>
       <c r="D29" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0883</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
         <v>10</v>
@@ -7805,19 +7281,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>WAI-SR</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.4684</v>
+        <v>0.2267</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1115</v>
+        <v>0.0717</v>
       </c>
       <c r="E30" t="n">
         <v>9</v>
@@ -7829,22 +7305,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>PTO_LA5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MIPROC</t>
+          <t>CSQ-8</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0388</v>
+        <v>0.2301</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0053</v>
+        <v>0.0728</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
         <v>10</v>
@@ -7858,17 +7334,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Q1Q2</t>
+          <t>MI-SAT</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.349</v>
+        <v>0.2215</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0883</v>
+        <v>0.0717</v>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F32" t="n">
         <v>10</v>
@@ -7882,17 +7358,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WAI-SR</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.2267</v>
+        <v>0.1305</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0717</v>
+        <v>0.0282</v>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
         <v>10</v>
@@ -7906,14 +7382,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CSQ-8</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.2301</v>
+        <v>0.1097</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0728</v>
+        <v>0.0149</v>
       </c>
       <c r="E34" t="n">
         <v>10</v>
@@ -7930,17 +7406,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MI-SAT</t>
+          <t>MICI</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.2215</v>
+        <v>0.2471</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0717</v>
+        <v>0.0247</v>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
         <v>10</v>
@@ -7954,17 +7430,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1305</v>
+        <v>0.337</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0282</v>
+        <v>0.1005</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
         <v>10</v>
@@ -7978,115 +7454,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.1097</v>
+        <v>0.3283</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0149</v>
+        <v>0.0762</v>
       </c>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>MICI</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.2471</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="E38" t="n">
-        <v>6</v>
-      </c>
-      <c r="F38" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.1005</v>
-      </c>
-      <c r="E39" t="n">
-        <v>7</v>
-      </c>
-      <c r="F39" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.3283</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.0762</v>
-      </c>
-      <c r="E40" t="n">
-        <v>9</v>
-      </c>
-      <c r="F40" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0.1347</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="E41" t="n">
-        <v>10</v>
-      </c>
-      <c r="F41" t="n">
         <v>10</v>
       </c>
     </row>
